--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.36682153896778</v>
+        <v>4.772108500082265</v>
       </c>
       <c r="D2" t="n">
-        <v>29.85188642987274</v>
+        <v>4.850931544854321</v>
       </c>
       <c r="E2" t="n">
-        <v>19.2810796450677</v>
+        <v>3.133175442323501</v>
       </c>
       <c r="F2" t="n">
-        <v>8.552206316371766</v>
+        <v>1.389733526410412</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.40040667952157</v>
+        <v>8.027566085422256</v>
       </c>
       <c r="D3" t="n">
-        <v>24.13503677229434</v>
+        <v>3.921943475497831</v>
       </c>
       <c r="E3" t="n">
-        <v>19.2810796450677</v>
+        <v>3.133175442323501</v>
       </c>
       <c r="F3" t="n">
-        <v>8.552206316371766</v>
+        <v>1.389733526410412</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.46858781501162</v>
+        <v>9.01364551993939</v>
       </c>
       <c r="D4" t="n">
-        <v>29.43637205907005</v>
+        <v>4.783410459598883</v>
       </c>
       <c r="E4" t="n">
-        <v>19.2810796450677</v>
+        <v>3.133175442323501</v>
       </c>
       <c r="F4" t="n">
-        <v>8.552206316371766</v>
+        <v>1.389733526410412</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.47463676179606</v>
+        <v>9.177128473791859</v>
       </c>
       <c r="D5" t="n">
-        <v>24.46716491148197</v>
+        <v>3.97591429811582</v>
       </c>
       <c r="E5" t="n">
-        <v>19.2810796450677</v>
+        <v>3.133175442323501</v>
       </c>
       <c r="F5" t="n">
-        <v>8.552206316371766</v>
+        <v>1.389733526410412</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.43960886147372</v>
+        <v>9.333936439989479</v>
       </c>
       <c r="D6" t="n">
-        <v>17.9349158935044</v>
+        <v>2.914423832694466</v>
       </c>
       <c r="E6" t="n">
-        <v>19.2810796450677</v>
+        <v>3.133175442323501</v>
       </c>
       <c r="F6" t="n">
-        <v>8.552206316371766</v>
+        <v>1.389733526410412</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.75708603590645</v>
+        <v>0.7730264808347981</v>
       </c>
       <c r="D7" t="n">
-        <v>4.823749021278832</v>
+        <v>0.7838592159578103</v>
       </c>
       <c r="E7" t="n">
-        <v>19.2810796450677</v>
+        <v>3.133175442323501</v>
       </c>
       <c r="F7" t="n">
-        <v>8.552206316371766</v>
+        <v>1.389733526410412</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
